--- a/sum_daily_order/result/Weekly_Performance_Report_VN.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,16 +42,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-01-21-18_39.csv</t>
-  </si>
-  <si>
-    <t>全部 笔订单-2026-01-22-18_43.csv</t>
-  </si>
-  <si>
-    <t>21/01/2026</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
+    <t>全部 笔订单-2026-02-11-09_52.csv</t>
+  </si>
+  <si>
+    <t>全部 笔订单-2026-02-12-09_54.csv</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>11/02/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -63,6 +63,9 @@
     <t>销售额</t>
   </si>
   <si>
+    <t>汇率后(销售额/3600)</t>
+  </si>
+  <si>
     <t>P列折后价</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>汇率后(销售额/3600)</t>
-  </si>
-  <si>
     <t>精华液</t>
   </si>
   <si>
@@ -87,6 +87,9 @@
     <t>身体乳300ml</t>
   </si>
   <si>
+    <t>防晒霜</t>
+  </si>
+  <si>
     <t>产品名称</t>
   </si>
   <si>
@@ -99,7 +102,19 @@
     <t>身体乳双瓶</t>
   </si>
   <si>
+    <t>防晒霜单瓶</t>
+  </si>
+  <si>
+    <t>防晒霜双瓶</t>
+  </si>
+  <si>
     <t>精华液单瓶</t>
+  </si>
+  <si>
+    <t>精华液双瓶</t>
+  </si>
+  <si>
+    <t>精华液&amp;黑鸦片</t>
   </si>
   <si>
     <t>汇总</t>
@@ -118,8 +133,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -133,12 +149,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -147,7 +178,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,28 +479,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -479,22 +512,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>1223753</v>
+        <v>1184388</v>
       </c>
       <c r="D2">
-        <v>339.93</v>
+        <v>329</v>
       </c>
       <c r="E2">
-        <v>1160703</v>
+        <v>989548</v>
       </c>
       <c r="F2">
-        <v>105.7</v>
+        <v>114.41</v>
       </c>
       <c r="G2">
-        <v>64.53</v>
+        <v>64.87</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -505,22 +538,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>623994</v>
+        <v>2419392</v>
       </c>
       <c r="D3">
-        <v>173.33</v>
+        <v>672.05</v>
       </c>
       <c r="E3">
-        <v>575494</v>
+        <v>2139392</v>
       </c>
       <c r="F3">
-        <v>59.23999999999999</v>
+        <v>161.31</v>
       </c>
       <c r="G3">
-        <v>39.35</v>
+        <v>65.89999999999999</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>60.63</v>
       </c>
     </row>
   </sheetData>
@@ -530,32 +563,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -567,22 +600,22 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>168163</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>168163</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>9.02</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>46.71</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -593,22 +626,22 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>968590</v>
+        <v>1029589</v>
       </c>
       <c r="D3">
-        <v>905540</v>
+        <v>286</v>
       </c>
       <c r="E3">
-        <v>93.59999999999999</v>
+        <v>849749</v>
       </c>
       <c r="F3">
-        <v>59.29</v>
+        <v>102.96</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>59.69</v>
       </c>
       <c r="H3">
-        <v>269.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -619,48 +652,48 @@
         <v>22</v>
       </c>
       <c r="C4">
-        <v>87000</v>
+        <v>52000</v>
       </c>
       <c r="D4">
-        <v>87000</v>
+        <v>14.44</v>
       </c>
       <c r="E4">
+        <v>52000</v>
+      </c>
+      <c r="F4">
         <v>3.08</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>2.03</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
-        <v>24.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>536994</v>
+        <v>102799</v>
       </c>
       <c r="D5">
-        <v>488494</v>
+        <v>28.56</v>
       </c>
       <c r="E5">
-        <v>56.16</v>
+        <v>87799</v>
       </c>
       <c r="F5">
-        <v>37.32</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
-        <v>149.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -668,25 +701,77 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>87000</v>
+        <v>1933557</v>
       </c>
       <c r="D6">
-        <v>87000</v>
+        <v>537.1</v>
       </c>
       <c r="E6">
-        <v>3.08</v>
+        <v>1678557</v>
       </c>
       <c r="F6">
-        <v>2.03</v>
+        <v>117.48</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>46.41</v>
       </c>
       <c r="H6">
-        <v>24.17</v>
+        <v>60.63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>197998</v>
+      </c>
+      <c r="D7">
+        <v>55</v>
+      </c>
+      <c r="E7">
+        <v>172998</v>
+      </c>
+      <c r="F7">
+        <v>18.72</v>
+      </c>
+      <c r="G7">
+        <v>12.44</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>287837</v>
+      </c>
+      <c r="D8">
+        <v>79.95</v>
+      </c>
+      <c r="E8">
+        <v>287837</v>
+      </c>
+      <c r="F8">
+        <v>25.11</v>
+      </c>
+      <c r="G8">
+        <v>7.05</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -696,73 +781,117 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>24</v>
+      <c r="A2" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>25</v>
+      <c r="A3" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>26</v>
+      <c r="A4" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>27</v>
+      <c r="A5" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="1" customFormat="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="1">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1">
-        <v>7</v>
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,16 +42,10 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-02-11-09_52.csv</t>
-  </si>
-  <si>
-    <t>全部 笔订单-2026-02-12-09_54.csv</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>11/02/2026</t>
+    <t>All order-2026-02-26-10_44.csv</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -78,22 +72,16 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>精华液</t>
-  </si>
-  <si>
     <t>身体乳</t>
   </si>
   <si>
     <t>身体乳300ml</t>
   </si>
   <si>
-    <t>防晒霜</t>
-  </si>
-  <si>
     <t>产品名称</t>
   </si>
   <si>
-    <t>身体乳300ml单瓶</t>
+    <t>身体乳300ml双瓶</t>
   </si>
   <si>
     <t>身体乳单瓶</t>
@@ -102,19 +90,7 @@
     <t>身体乳双瓶</t>
   </si>
   <si>
-    <t>防晒霜单瓶</t>
-  </si>
-  <si>
-    <t>防晒霜双瓶</t>
-  </si>
-  <si>
-    <t>精华液单瓶</t>
-  </si>
-  <si>
-    <t>精华液双瓶</t>
-  </si>
-  <si>
-    <t>精华液&amp;黑鸦片</t>
+    <t>身体乳三瓶</t>
   </si>
   <si>
     <t>汇总</t>
@@ -475,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -509,51 +485,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>1184388</v>
+        <v>531191</v>
       </c>
       <c r="D2">
-        <v>329</v>
+        <v>147.55</v>
       </c>
       <c r="E2">
-        <v>989548</v>
+        <v>531191</v>
       </c>
       <c r="F2">
-        <v>114.41</v>
+        <v>62.31999999999999</v>
       </c>
       <c r="G2">
-        <v>64.87</v>
+        <v>32.91</v>
       </c>
       <c r="H2">
-        <v>60.63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>2419392</v>
-      </c>
-      <c r="D3">
-        <v>672.05</v>
-      </c>
-      <c r="E3">
-        <v>2139392</v>
-      </c>
-      <c r="F3">
-        <v>161.31</v>
-      </c>
-      <c r="G3">
-        <v>65.89999999999999</v>
-      </c>
-      <c r="H3">
-        <v>60.63</v>
+        <v>42.36</v>
       </c>
     </row>
   </sheetData>
@@ -563,215 +513,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2">
+        <v>448064</v>
+      </c>
+      <c r="D2">
+        <v>124.46</v>
+      </c>
+      <c r="E2">
+        <v>448064</v>
+      </c>
+      <c r="F2">
+        <v>56.16</v>
+      </c>
+      <c r="G2">
+        <v>28.85</v>
+      </c>
+      <c r="H2">
         <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>60.63</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>1029589</v>
+        <v>83127</v>
       </c>
       <c r="D3">
-        <v>286</v>
+        <v>23.09</v>
       </c>
       <c r="E3">
-        <v>849749</v>
+        <v>83127</v>
       </c>
       <c r="F3">
-        <v>102.96</v>
+        <v>6.16</v>
       </c>
       <c r="G3">
-        <v>59.69</v>
+        <v>4.06</v>
       </c>
       <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4">
-        <v>52000</v>
-      </c>
-      <c r="D4">
-        <v>14.44</v>
-      </c>
-      <c r="E4">
-        <v>52000</v>
-      </c>
-      <c r="F4">
-        <v>3.08</v>
-      </c>
-      <c r="G4">
-        <v>2.03</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5">
-        <v>102799</v>
-      </c>
-      <c r="D5">
-        <v>28.56</v>
-      </c>
-      <c r="E5">
-        <v>87799</v>
-      </c>
-      <c r="F5">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="G5">
-        <v>3.15</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>1933557</v>
-      </c>
-      <c r="D6">
-        <v>537.1</v>
-      </c>
-      <c r="E6">
-        <v>1678557</v>
-      </c>
-      <c r="F6">
-        <v>117.48</v>
-      </c>
-      <c r="G6">
-        <v>46.41</v>
-      </c>
-      <c r="H6">
-        <v>60.63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7">
-        <v>197998</v>
-      </c>
-      <c r="D7">
-        <v>55</v>
-      </c>
-      <c r="E7">
-        <v>172998</v>
-      </c>
-      <c r="F7">
-        <v>18.72</v>
-      </c>
-      <c r="G7">
-        <v>12.44</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>287837</v>
-      </c>
-      <c r="D8">
-        <v>79.95</v>
-      </c>
-      <c r="E8">
-        <v>287837</v>
-      </c>
-      <c r="F8">
-        <v>25.11</v>
-      </c>
-      <c r="G8">
-        <v>7.05</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>42.36</v>
       </c>
     </row>
   </sheetData>
@@ -781,117 +601,55 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-      <c r="C10">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
